--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F758C5A3-1F95-41A7-8F85-7D38A68BEF4D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E957B654-D249-44E7-9DF1-BBBCBF61BA19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="162">
   <si>
     <t>index</t>
   </si>
@@ -461,12 +461,6 @@
   </si>
   <si>
     <t>migration_T3</t>
-  </si>
-  <si>
-    <t>atc_who_2010</t>
-  </si>
-  <si>
-    <t>undetermined</t>
   </si>
   <si>
     <t>recode(0=0;1=1;2=1;)</t>
@@ -484,9 +478,6 @@
 If both parents are "not at all employed," assign 5L.
 If one parent's status is NA, use the other parent's status to determine the category.
 If both are NA, assign 7L ("other").</t>
-  </si>
-  <si>
-    <t>SED;LPA;MPA;VPA</t>
   </si>
   <si>
     <t>chdiabet</t>
@@ -508,17 +499,32 @@
     <t>phys_activ;leis_activ</t>
   </si>
   <si>
-    <t>(4 * phys_activ + 1.5 * leis_activ) / 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">((1.5 * SED)/60 + (1.5 * LPA)/60 + (3 * MPA)/60 + (6 * VPA)/60) </t>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>proximate</t>
+  </si>
+  <si>
+    <t>LPA;MPA;VPA</t>
+  </si>
+  <si>
+    <t>To be generated by DHO</t>
+  </si>
+  <si>
+    <t>6.17 * (phys_activ + leis_activ) / 7</t>
+  </si>
+  <si>
+    <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities</t>
+  </si>
+  <si>
+    <t>(1.5 * LPA + 3 * MPA + 6 * VPA) / 60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,20 +549,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -581,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -590,26 +588,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -956,7 +955,7 @@
     <col min="3" max="3" width="54" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
     <col min="7" max="7" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="48" customWidth="1"/>
     <col min="9" max="9" width="38.140625" customWidth="1"/>
@@ -1077,55 +1076,58 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="H5" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="1:11" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="H6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1152,84 +1154,84 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="4" customFormat="1" ht="195" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="195" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="H9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="J10" s="4" t="s">
+      <c r="H10" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1243,7 +1245,7 @@
       <c r="D11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="4"/>
       <c r="G11" t="s">
         <v>144</v>
       </c>
@@ -1267,7 +1269,7 @@
       <c r="D12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="4"/>
       <c r="G12" t="s">
         <v>144</v>
       </c>
@@ -1291,7 +1293,7 @@
       <c r="D13" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="4"/>
       <c r="G13" t="s">
         <v>144</v>
       </c>
@@ -1305,30 +1307,33 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>148</v>
+        <v>37</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1446,29 +1451,29 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
+    <row r="20" spans="2:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="D20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="5" t="s">
         <v>136</v>
       </c>
     </row>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E957B654-D249-44E7-9DF1-BBBCBF61BA19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7361C21A-BD08-410C-9C31-402490C9E372}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -472,52 +472,70 @@
     <t>occupst_1;occupst_2</t>
   </si>
   <si>
+    <t>chdiabet</t>
+  </si>
+  <si>
+    <t>recode(0=0;1=1;2=2;3=3;4=4;5=5;6=7;)</t>
+  </si>
+  <si>
+    <t>phys_activ;leis_activ</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>proximate</t>
+  </si>
+  <si>
+    <t>LPA;MPA;VPA</t>
+  </si>
+  <si>
+    <t>To be generated by DHO</t>
+  </si>
+  <si>
+    <t>6.17 * (phys_activ + leis_activ) / 7</t>
+  </si>
+  <si>
+    <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities</t>
+  </si>
+  <si>
+    <t>(1.5 * LPA + 3 * MPA + 6 * VPA) / 60</t>
+  </si>
+  <si>
+    <t>occupation_level &lt;- case_when(
+  occupst_1 %in% 1 | occupst_2 %in% 1 ~ 1L, 
+  occupst_1 %in% 2 | occupst_2 %in% 2 ~ 2L, 
+  occupst_1 %in% 4 &amp; occupst_2 %in% 4 ~ 3L, 
+  occupst_1 %in% 5 &amp; occupst_2 %in% 5 ~ 4L,        
+  is.na(occupst_1) &amp; occupst_2 %in% 5 ~ 4L, 
+  is.na(occupst_2) &amp; occupst_1 %in% 5 ~ 4L,  
+  (occupst_1 %in% 4 &amp; occupst_2 %in% 3) | (occupst_1 %in% 3 &amp; occupst_2 %in% 4)  ~ 4L,
+  (occupst_1 %in% 4 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 4) ~ 4L, 
+  (occupst_1 %in% 4 &amp; occupst_2 %in% 6) | (occupst_1 %in% 6 &amp; occupst_2 %in% 4) ~ 4L,
+  occupst_1 %in% c(7,8,9) &amp; occupst_2 %in% c(7,8,9) ~ 5L, 
+  is.na(occupst_1) &amp; occupst_2 %in% c(7,8,9) ~ 5L,
+  is.na(occupst_2) &amp; occupst_1 %in% c(7,8,9) ~ 5L,  
+  (occupst_1 %in% 3 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 3) ~ 5L,     
+  (occupst_1 %in% 6 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 6) ~ 5L,   
+  occupst_1 %in% 3 &amp; occupst_2 %in% 3 ~ 6L,   
+  is.na(occupst_1) &amp; occupst_2 %in% 3 ~ 6L,   
+  is.na(occupst_2) &amp; occupst_1 %in% 3 ~ 6L,   
+  (occupst_1 %in% 3 &amp; occupst_2 %in% 6) | (occupst_1 %in% 6 &amp; occupst_2 %in% 3) ~ 6L, 
+  occupst_1 %in% c(6,10) | occupst_2 %in% c(6,10) ~ 7L,         
+  is.na(occupst_1) &amp; is.na(occupst_2) ~ 7L,
+  (occupst_1 %in% 3 &amp; occupst_2 %in% 10) | (occupst_1 %in% 10 &amp; occupst_2 %in% 3) ~ 7L, 
+  (occupst_1 %in% 6 &amp; occupst_2 %in% 10) | (occupst_1 %in% 10 &amp; occupst_2 %in% 6) ~ 7L,  
+  (occupst_1 %in% 5 &amp; occupst_2 %in% 10) | (occupst_1 %in% 10 &amp; occupst_2 %in% 5) ~ 7L,  
+  TRUE ~ NA_integer_
+)</t>
+  </si>
+  <si>
     <t xml:space="preserve">
-If either parent is "fully employed (100%)," assign 1L.
-If either parent works "more than half day," "half day," or "less than half day,"  assign 2L.
-If both parents are "not at all employed," assign 5L.
-If one parent's status is NA, use the other parent's status to determine the category.
-If both are NA, assign 7L ("other").</t>
-  </si>
-  <si>
-    <t>chdiabet</t>
-  </si>
-  <si>
-    <t>recode(0=0;1=1;2=2;3=3;4=4;5=5;6=7;)</t>
-  </si>
-  <si>
-    <t>case_when(
-      occupst_1 == c(1)|occupst_2== c(1) ~ 1L,
-      occupst_1==c(2)|occupst_2==c(2) ~ 2L,  
-      occupst_1 == c(4)&amp;occupst_2==(4)~ 3L,
-     occupst_1 == c(5)&amp;occupst_2== c(5) ~ 4L,                                                                                                    occupst_1 %in% c(7,8,9) &amp;occupst_2%in%c(7,8,9) ~ 5L,                                                                                            occupst_1 ==c(3)&amp; occupst_2==c(3)~ 6L,                                                                                        occupst_1 ==c(6,10) &amp;  occupst_2==c(6,10) ~ 7L,                                                                                  is.na(occupst_1)&amp;occupst_2== c(5) ~ 5L,
-      is.na(occupst_2) &amp; occupst_1== c(5) ~ 5L,
-      is.na(occupst_1) &amp; is.na(occupst_2) ~ 7L,
-      TRUE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>phys_activ;leis_activ</t>
-  </si>
-  <si>
-    <t>partial</t>
-  </si>
-  <si>
-    <t>proximate</t>
-  </si>
-  <si>
-    <t>LPA;MPA;VPA</t>
-  </si>
-  <si>
-    <t>To be generated by DHO</t>
-  </si>
-  <si>
-    <t>6.17 * (phys_activ + leis_activ) / 7</t>
-  </si>
-  <si>
-    <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities</t>
-  </si>
-  <si>
-    <t>(1.5 * LPA + 3 * MPA + 6 * VPA) / 60</t>
+# If either parent is "fully employed (100%)," assign 1L.
+# If either parent works "more than half day," "half day," or "less than half day,"  assign 2L.
+# If both parents are "are home markers," assign 3L.                                                                   # If both parents are "retired," assign 4L.                                                                  # If both parents are "not at all employed," assign 5L.
+# If one parent's status is NA, use the other parent's status to determine the category. # If one parent's status is lower, use the other parent's higher-status to determine the category. 
+# If both are NA, assign 7L ("other").</t>
   </si>
 </sst>
 </file>
@@ -956,8 +974,8 @@
     <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" customWidth="1"/>
+    <col min="8" max="8" width="58.28515625" customWidth="1"/>
     <col min="9" max="9" width="38.140625" customWidth="1"/>
     <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -1093,7 +1111,7 @@
         <v>142</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>135</v>
@@ -1113,16 +1131,16 @@
         <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>143</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>135</v>
@@ -1154,7 +1172,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" ht="195" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
@@ -1171,10 +1189,10 @@
         <v>148</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>135</v>
@@ -1220,13 +1238,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>143</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>135</v>
@@ -1327,13 +1345,13 @@
         <v>134</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1462,7 +1480,7 @@
         <v>13</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>134</v>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7361C21A-BD08-410C-9C31-402490C9E372}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3395E231-3BCF-41DF-ABE4-115738D0E0EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="159">
   <si>
     <t>index</t>
   </si>
@@ -481,16 +481,7 @@
     <t>phys_activ;leis_activ</t>
   </si>
   <si>
-    <t>partial</t>
-  </si>
-  <si>
-    <t>proximate</t>
-  </si>
-  <si>
     <t>LPA;MPA;VPA</t>
-  </si>
-  <si>
-    <t>To be generated by DHO</t>
   </si>
   <si>
     <t>6.17 * (phys_activ + leis_activ) / 7</t>
@@ -1137,10 +1128,10 @@
         <v>143</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>135</v>
@@ -1189,10 +1180,10 @@
         <v>148</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>135</v>
@@ -1238,13 +1229,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>143</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>135</v>
@@ -1335,23 +1326,17 @@
       <c r="D14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="G14" s="5" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3395E231-3BCF-41DF-ABE4-115738D0E0EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D5DEED-C0B1-4ADF-9EFF-D4B253398FC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,6 +493,14 @@
     <t>(1.5 * LPA + 3 * MPA + 6 * VPA) / 60</t>
   </si>
   <si>
+    <t xml:space="preserve">
+# If either parent is "fully employed (100%)," assign 1L.
+# If either parent works "more than half day," "half day," or "less than half day,"  assign 2L.
+# If both parents are "are home markers," assign 3L.                                                                   # If both parents are "retired," assign 4L.                                                                  # If both parents are "not at all employed," assign 5L.
+# If one parent's status is NA, use the other parent's status to determine the category. # If one parent's status is lower, use the other parent's higher-status to determine the category. 
+# If both are NA, assign 7L ("other").</t>
+  </si>
+  <si>
     <t>occupation_level &lt;- case_when(
   occupst_1 %in% 1 | occupst_2 %in% 1 ~ 1L, 
   occupst_1 %in% 2 | occupst_2 %in% 2 ~ 2L, 
@@ -500,33 +508,22 @@
   occupst_1 %in% 5 &amp; occupst_2 %in% 5 ~ 4L,        
   is.na(occupst_1) &amp; occupst_2 %in% 5 ~ 4L, 
   is.na(occupst_2) &amp; occupst_1 %in% 5 ~ 4L,  
-  (occupst_1 %in% 4 &amp; occupst_2 %in% 3) | (occupst_1 %in% 3 &amp; occupst_2 %in% 4)  ~ 4L,
+  (occupst_1 %in% 4 &amp; occupst_2 %in% 3) | (occupst_1 %in% 3 &amp; occupst_2 %in% 4)  ~ 6L,
   (occupst_1 %in% 4 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 4) ~ 4L, 
-  (occupst_1 %in% 4 &amp; occupst_2 %in% 6) | (occupst_1 %in% 6 &amp; occupst_2 %in% 4) ~ 4L,
+  (occupst_1 %in% 4 &amp; occupst_2 %in% 6) | (occupst_1 %in% 6 &amp; occupst_2 %in% 4) ~ 7L,
   occupst_1 %in% c(7,8,9) &amp; occupst_2 %in% c(7,8,9) ~ 5L, 
   is.na(occupst_1) &amp; occupst_2 %in% c(7,8,9) ~ 5L,
   is.na(occupst_2) &amp; occupst_1 %in% c(7,8,9) ~ 5L,  
-  (occupst_1 %in% 3 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 3) ~ 5L,     
-  (occupst_1 %in% 6 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 6) ~ 5L,   
+  (occupst_1 %in% 3 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 3) ~ 4L,     
+  (occupst_1 %in% 6 &amp; occupst_2 %in% 5) | (occupst_1 %in% 5 &amp; occupst_2 %in% 6) ~ 7L,   
   occupst_1 %in% 3 &amp; occupst_2 %in% 3 ~ 6L,   
   is.na(occupst_1) &amp; occupst_2 %in% 3 ~ 6L,   
   is.na(occupst_2) &amp; occupst_1 %in% 3 ~ 6L,   
-  (occupst_1 %in% 3 &amp; occupst_2 %in% 6) | (occupst_1 %in% 6 &amp; occupst_2 %in% 3) ~ 6L, 
+  (occupst_1 %in% 3 &amp; occupst_2 %in% 6) | (occupst_1 %in% 6 &amp; occupst_2 %in% 3) ~ 7L, 
   occupst_1 %in% c(6,10) | occupst_2 %in% c(6,10) ~ 7L,         
-  is.na(occupst_1) &amp; is.na(occupst_2) ~ 7L,
-  (occupst_1 %in% 3 &amp; occupst_2 %in% 10) | (occupst_1 %in% 10 &amp; occupst_2 %in% 3) ~ 7L, 
-  (occupst_1 %in% 6 &amp; occupst_2 %in% 10) | (occupst_1 %in% 10 &amp; occupst_2 %in% 6) ~ 7L,  
-  (occupst_1 %in% 5 &amp; occupst_2 %in% 10) | (occupst_1 %in% 10 &amp; occupst_2 %in% 5) ~ 7L,  
+  is.na(occupst_1) &amp; is.na(occupst_2) ~ 7L,                                   occupst_1 %in% 10 &amp; occupst_2 %in% 10 ~ 7L,                          occupst_1 %in% 10 &amp; occupst_2 %in% c(1:9) ~ 1L,                    occupst_1 %in% c(1:9) &amp; occupst_2 %in% 10 ~ 1L,                     
   TRUE ~ NA_integer_
 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-# If either parent is "fully employed (100%)," assign 1L.
-# If either parent works "more than half day," "half day," or "less than half day,"  assign 2L.
-# If both parents are "are home markers," assign 3L.                                                                   # If both parents are "retired," assign 4L.                                                                  # If both parents are "not at all employed," assign 5L.
-# If one parent's status is NA, use the other parent's status to determine the category. # If one parent's status is lower, use the other parent's higher-status to determine the category. 
-# If both are NA, assign 7L ("other").</t>
   </si>
 </sst>
 </file>
@@ -1180,10 +1177,10 @@
         <v>148</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>158</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>135</v>
@@ -1326,16 +1323,16 @@
       <c r="D14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="K14" s="5" t="s">
+      <c r="G14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H14" t="s">
+        <v>144</v>
+      </c>
+      <c r="J14" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" t="s">
         <v>145</v>
       </c>
     </row>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_IDEFICS_TRACY.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D5DEED-C0B1-4ADF-9EFF-D4B253398FC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F1DD37-BC56-4100-B678-9A4B8EE7132E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="167">
   <si>
     <t>index</t>
   </si>
@@ -475,19 +480,7 @@
     <t>chdiabet</t>
   </si>
   <si>
-    <t>recode(0=0;1=1;2=2;3=3;4=4;5=5;6=7;)</t>
-  </si>
-  <si>
-    <t>phys_activ;leis_activ</t>
-  </si>
-  <si>
     <t>LPA;MPA;VPA</t>
-  </si>
-  <si>
-    <t>6.17 * (phys_activ + leis_activ) / 7</t>
-  </si>
-  <si>
-    <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities</t>
   </si>
   <si>
     <t>(1.5 * LPA + 3 * MPA + 6 * VPA) / 60</t>
@@ -524,6 +517,49 @@
   is.na(occupst_1) &amp; is.na(occupst_2) ~ 7L,                                   occupst_1 %in% 10 &amp; occupst_2 %in% 10 ~ 7L,                          occupst_1 %in% 10 &amp; occupst_2 %in% c(1:9) ~ 1L,                    occupst_1 %in% c(1:9) &amp; occupst_2 %in% 10 ~ 1L,                     
   TRUE ~ NA_integer_
 )</t>
+  </si>
+  <si>
+    <t>6.0 * phys_activ / 7</t>
+  </si>
+  <si>
+    <t>phys_activ</t>
+  </si>
+  <si>
+    <t>The average MET value of children between 6 to 15years was determined according to NCCOR Compendium.METy Values (Smoothed) – View All Categories - NCCOR Youth Compendium of Physical Activities; FS-TOB: formula changed to reflect children ages 6-9 and reduce overlap (dropping leis_activ)</t>
+  </si>
+  <si>
+    <t>recode(0=0;1=1;2=2;3=3;4=4;5=7;6=8;9=9)</t>
+  </si>
+  <si>
+    <t>FS: addresses correct ISCED-1997 levels</t>
+  </si>
+  <si>
+    <t>ID_cohort</t>
+  </si>
+  <si>
+    <t>case_when(_x000D_
+  sex_child == 1 ~ 1L, _x000D_
+  sex_child == 2 ~ 2L, _x000D_
+  TRUE ~ NA_integer__x000D_
+)</t>
+  </si>
+  <si>
+    <t>FS: there are categories 0,3 and 9 which are not male or female</t>
+  </si>
+  <si>
+    <t>case_when(_x000D_
+  chdiabet == 1 ~ 1L, _x000D_
+  TRUE ~ 0L_x000D_
+)</t>
+  </si>
+  <si>
+    <t>FS: The variable is either 1 (yes) OR NA (no or missing)</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>proximate</t>
   </si>
 </sst>
 </file>
@@ -585,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -613,12 +649,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -634,9 +667,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -674,9 +707,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -709,26 +742,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -761,26 +777,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -955,7 +954,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54" bestFit="1" customWidth="1"/>
@@ -1015,7 +1014,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s">
         <v>138</v>
@@ -1044,10 +1043,13 @@
         <v>137</v>
       </c>
       <c r="G3" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H3" t="s">
-        <v>134</v>
+        <v>161</v>
+      </c>
+      <c r="I3" t="s">
+        <v>162</v>
       </c>
       <c r="J3" t="s">
         <v>135</v>
@@ -1092,23 +1094,26 @@
       <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" t="s">
         <v>140</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>151</v>
+      <c r="H5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I5" t="s">
+        <v>159</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
@@ -1119,22 +1124,22 @@
         <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>143</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1177,16 +1182,16 @@
         <v>148</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1226,13 +1231,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>143</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>135</v>
@@ -1461,14 +1466,17 @@
       <c r="D20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" t="s">
         <v>150</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>134</v>
+      <c r="G20" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" t="s">
+        <v>164</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>135</v>
